--- a/Intelligent_Sourcing.xlsx
+++ b/Intelligent_Sourcing.xlsx
@@ -14,15 +14,13 @@
     <sheet name="Cost Data" sheetId="5" r:id="rId5"/>
     <sheet name="Distance Data" sheetId="6" r:id="rId6"/>
     <sheet name="Days Data" sheetId="7" r:id="rId7"/>
-    <sheet name="Fulfillment Solution" sheetId="8" r:id="rId8"/>
-    <sheet name="Warehouse Stock Status" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="25">
   <si>
     <t>Variable</t>
   </si>
@@ -87,9 +85,6 @@
     <t>Product#10</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>Order</t>
   </si>
   <si>
@@ -100,18 +95,6 @@
   </si>
   <si>
     <t>Product</t>
-  </si>
-  <si>
-    <t>Supply Quantity</t>
-  </si>
-  <si>
-    <t>Initial Stock</t>
-  </si>
-  <si>
-    <t>Supplied Stock</t>
-  </si>
-  <si>
-    <t>Remaining Stock</t>
   </si>
 </sst>
 </file>
@@ -649,8 +632,8 @@
       <c r="B3">
         <v>86</v>
       </c>
-      <c r="C3" t="s">
-        <v>21</v>
+      <c r="C3">
+        <v>10</v>
       </c>
       <c r="D3">
         <v>76</v>
@@ -759,7 +742,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>11</v>
@@ -794,7 +777,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -829,7 +812,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>9</v>
@@ -877,10 +860,10 @@
         <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -891,7 +874,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -905,7 +888,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -919,7 +902,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -933,7 +916,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
@@ -947,7 +930,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -961,7 +944,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
@@ -975,7 +958,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -989,7 +972,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -1003,7 +986,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
@@ -1017,7 +1000,7 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
@@ -1031,7 +1014,7 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
@@ -1045,7 +1028,7 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -1059,7 +1042,7 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
@@ -1073,7 +1056,7 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
@@ -1087,7 +1070,7 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
@@ -1101,7 +1084,7 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
@@ -1115,7 +1098,7 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
         <v>17</v>
@@ -1129,7 +1112,7 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
@@ -1143,7 +1126,7 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
         <v>19</v>
@@ -1157,7 +1140,7 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
         <v>20</v>
@@ -1171,7 +1154,7 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
@@ -1185,7 +1168,7 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -1199,7 +1182,7 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
         <v>13</v>
@@ -1213,7 +1196,7 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
         <v>14</v>
@@ -1227,7 +1210,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
         <v>15</v>
@@ -1241,7 +1224,7 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C27" t="s">
         <v>16</v>
@@ -1255,7 +1238,7 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
         <v>17</v>
@@ -1269,7 +1252,7 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
         <v>18</v>
@@ -1283,7 +1266,7 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C30" t="s">
         <v>19</v>
@@ -1297,7 +1280,7 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C31" t="s">
         <v>20</v>
@@ -1311,7 +1294,7 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -1325,7 +1308,7 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
@@ -1339,7 +1322,7 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
@@ -1353,7 +1336,7 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
@@ -1367,7 +1350,7 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
@@ -1381,7 +1364,7 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
         <v>16</v>
@@ -1395,7 +1378,7 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C38" t="s">
         <v>17</v>
@@ -1409,7 +1392,7 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
@@ -1423,7 +1406,7 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C40" t="s">
         <v>19</v>
@@ -1437,7 +1420,7 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C41" t="s">
         <v>20</v>
@@ -1451,7 +1434,7 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
@@ -1465,7 +1448,7 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
@@ -1479,7 +1462,7 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
@@ -1493,7 +1476,7 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
@@ -1507,7 +1490,7 @@
         <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C46" t="s">
         <v>15</v>
@@ -1521,7 +1504,7 @@
         <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C47" t="s">
         <v>16</v>
@@ -1535,7 +1518,7 @@
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C48" t="s">
         <v>17</v>
@@ -1549,7 +1532,7 @@
         <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C49" t="s">
         <v>18</v>
@@ -1563,7 +1546,7 @@
         <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C50" t="s">
         <v>19</v>
@@ -1577,7 +1560,7 @@
         <v>9</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C51" t="s">
         <v>20</v>
@@ -1591,7 +1574,7 @@
         <v>9</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C52" t="s">
         <v>11</v>
@@ -1605,7 +1588,7 @@
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C53" t="s">
         <v>12</v>
@@ -1619,7 +1602,7 @@
         <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C54" t="s">
         <v>13</v>
@@ -1633,7 +1616,7 @@
         <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
@@ -1647,7 +1630,7 @@
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C56" t="s">
         <v>15</v>
@@ -1661,7 +1644,7 @@
         <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C57" t="s">
         <v>16</v>
@@ -1675,7 +1658,7 @@
         <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C58" t="s">
         <v>17</v>
@@ -1689,7 +1672,7 @@
         <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C59" t="s">
         <v>18</v>
@@ -1703,7 +1686,7 @@
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C60" t="s">
         <v>19</v>
@@ -1717,7 +1700,7 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C61" t="s">
         <v>20</v>
@@ -1731,7 +1714,7 @@
         <v>10</v>
       </c>
       <c r="B62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C62" t="s">
         <v>11</v>
@@ -1745,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="B63" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C63" t="s">
         <v>12</v>
@@ -1759,7 +1742,7 @@
         <v>10</v>
       </c>
       <c r="B64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C64" t="s">
         <v>13</v>
@@ -1773,7 +1756,7 @@
         <v>10</v>
       </c>
       <c r="B65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -1787,7 +1770,7 @@
         <v>10</v>
       </c>
       <c r="B66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C66" t="s">
         <v>15</v>
@@ -1801,7 +1784,7 @@
         <v>10</v>
       </c>
       <c r="B67" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C67" t="s">
         <v>16</v>
@@ -1815,7 +1798,7 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C68" t="s">
         <v>17</v>
@@ -1829,7 +1812,7 @@
         <v>10</v>
       </c>
       <c r="B69" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C69" t="s">
         <v>18</v>
@@ -1843,7 +1826,7 @@
         <v>10</v>
       </c>
       <c r="B70" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C70" t="s">
         <v>19</v>
@@ -1857,7 +1840,7 @@
         <v>10</v>
       </c>
       <c r="B71" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C71" t="s">
         <v>20</v>
@@ -1871,7 +1854,7 @@
         <v>10</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
@@ -1885,7 +1868,7 @@
         <v>10</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C73" t="s">
         <v>12</v>
@@ -1899,7 +1882,7 @@
         <v>10</v>
       </c>
       <c r="B74" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C74" t="s">
         <v>13</v>
@@ -1913,7 +1896,7 @@
         <v>10</v>
       </c>
       <c r="B75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
@@ -1927,7 +1910,7 @@
         <v>10</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C76" t="s">
         <v>15</v>
@@ -1941,7 +1924,7 @@
         <v>10</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C77" t="s">
         <v>16</v>
@@ -1955,7 +1938,7 @@
         <v>10</v>
       </c>
       <c r="B78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C78" t="s">
         <v>17</v>
@@ -1969,7 +1952,7 @@
         <v>10</v>
       </c>
       <c r="B79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C79" t="s">
         <v>18</v>
@@ -1983,7 +1966,7 @@
         <v>10</v>
       </c>
       <c r="B80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C80" t="s">
         <v>19</v>
@@ -1997,7 +1980,7 @@
         <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C81" t="s">
         <v>20</v>
@@ -2021,10 +2004,10 @@
         <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
@@ -2035,7 +2018,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -2049,7 +2032,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -2063,7 +2046,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -2077,7 +2060,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
@@ -2091,7 +2074,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -2105,7 +2088,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
@@ -2119,7 +2102,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -2133,7 +2116,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2147,7 +2130,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
@@ -2161,7 +2144,7 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
@@ -2175,7 +2158,7 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
@@ -2189,7 +2172,7 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -2203,7 +2186,7 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
@@ -2217,7 +2200,7 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
@@ -2231,7 +2214,7 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
@@ -2245,7 +2228,7 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
@@ -2259,7 +2242,7 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
         <v>17</v>
@@ -2273,7 +2256,7 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
@@ -2287,7 +2270,7 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
         <v>19</v>
@@ -2301,7 +2284,7 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
         <v>20</v>
@@ -2315,7 +2298,7 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
@@ -2329,7 +2312,7 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -2343,7 +2326,7 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
         <v>13</v>
@@ -2357,7 +2340,7 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
         <v>14</v>
@@ -2371,7 +2354,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
         <v>15</v>
@@ -2385,7 +2368,7 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C27" t="s">
         <v>16</v>
@@ -2399,7 +2382,7 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
         <v>17</v>
@@ -2413,7 +2396,7 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
         <v>18</v>
@@ -2427,7 +2410,7 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C30" t="s">
         <v>19</v>
@@ -2441,7 +2424,7 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C31" t="s">
         <v>20</v>
@@ -2455,7 +2438,7 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -2469,7 +2452,7 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
@@ -2483,7 +2466,7 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
@@ -2497,7 +2480,7 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
@@ -2511,7 +2494,7 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
@@ -2525,7 +2508,7 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
         <v>16</v>
@@ -2539,7 +2522,7 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C38" t="s">
         <v>17</v>
@@ -2553,7 +2536,7 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
@@ -2567,7 +2550,7 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C40" t="s">
         <v>19</v>
@@ -2581,7 +2564,7 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C41" t="s">
         <v>20</v>
@@ -2595,7 +2578,7 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
@@ -2609,7 +2592,7 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
@@ -2623,7 +2606,7 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
@@ -2637,7 +2620,7 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
@@ -2651,7 +2634,7 @@
         <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C46" t="s">
         <v>15</v>
@@ -2665,7 +2648,7 @@
         <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C47" t="s">
         <v>16</v>
@@ -2679,7 +2662,7 @@
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C48" t="s">
         <v>17</v>
@@ -2693,7 +2676,7 @@
         <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C49" t="s">
         <v>18</v>
@@ -2707,7 +2690,7 @@
         <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C50" t="s">
         <v>19</v>
@@ -2721,7 +2704,7 @@
         <v>9</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C51" t="s">
         <v>20</v>
@@ -2735,7 +2718,7 @@
         <v>9</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C52" t="s">
         <v>11</v>
@@ -2749,7 +2732,7 @@
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C53" t="s">
         <v>12</v>
@@ -2763,7 +2746,7 @@
         <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C54" t="s">
         <v>13</v>
@@ -2777,7 +2760,7 @@
         <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
@@ -2791,7 +2774,7 @@
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C56" t="s">
         <v>15</v>
@@ -2805,7 +2788,7 @@
         <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C57" t="s">
         <v>16</v>
@@ -2819,7 +2802,7 @@
         <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C58" t="s">
         <v>17</v>
@@ -2833,7 +2816,7 @@
         <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C59" t="s">
         <v>18</v>
@@ -2847,7 +2830,7 @@
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C60" t="s">
         <v>19</v>
@@ -2861,7 +2844,7 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C61" t="s">
         <v>20</v>
@@ -2875,7 +2858,7 @@
         <v>10</v>
       </c>
       <c r="B62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C62" t="s">
         <v>11</v>
@@ -2889,7 +2872,7 @@
         <v>10</v>
       </c>
       <c r="B63" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C63" t="s">
         <v>12</v>
@@ -2903,7 +2886,7 @@
         <v>10</v>
       </c>
       <c r="B64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C64" t="s">
         <v>13</v>
@@ -2917,7 +2900,7 @@
         <v>10</v>
       </c>
       <c r="B65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -2931,7 +2914,7 @@
         <v>10</v>
       </c>
       <c r="B66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C66" t="s">
         <v>15</v>
@@ -2945,7 +2928,7 @@
         <v>10</v>
       </c>
       <c r="B67" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C67" t="s">
         <v>16</v>
@@ -2959,7 +2942,7 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C68" t="s">
         <v>17</v>
@@ -2973,7 +2956,7 @@
         <v>10</v>
       </c>
       <c r="B69" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C69" t="s">
         <v>18</v>
@@ -2987,7 +2970,7 @@
         <v>10</v>
       </c>
       <c r="B70" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C70" t="s">
         <v>19</v>
@@ -3001,7 +2984,7 @@
         <v>10</v>
       </c>
       <c r="B71" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C71" t="s">
         <v>20</v>
@@ -3015,7 +2998,7 @@
         <v>10</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
@@ -3029,7 +3012,7 @@
         <v>10</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C73" t="s">
         <v>12</v>
@@ -3043,7 +3026,7 @@
         <v>10</v>
       </c>
       <c r="B74" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C74" t="s">
         <v>13</v>
@@ -3057,7 +3040,7 @@
         <v>10</v>
       </c>
       <c r="B75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
@@ -3071,7 +3054,7 @@
         <v>10</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C76" t="s">
         <v>15</v>
@@ -3085,7 +3068,7 @@
         <v>10</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C77" t="s">
         <v>16</v>
@@ -3099,7 +3082,7 @@
         <v>10</v>
       </c>
       <c r="B78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C78" t="s">
         <v>17</v>
@@ -3113,7 +3096,7 @@
         <v>10</v>
       </c>
       <c r="B79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C79" t="s">
         <v>18</v>
@@ -3127,7 +3110,7 @@
         <v>10</v>
       </c>
       <c r="B80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C80" t="s">
         <v>19</v>
@@ -3141,7 +3124,7 @@
         <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C81" t="s">
         <v>20</v>
@@ -3165,10 +3148,10 @@
         <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>5</v>
@@ -3179,7 +3162,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -3193,7 +3176,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -3207,7 +3190,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -3221,7 +3204,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
@@ -3235,7 +3218,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -3249,7 +3232,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
@@ -3263,7 +3246,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -3277,7 +3260,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -3291,7 +3274,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
@@ -3305,7 +3288,7 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
@@ -3319,7 +3302,7 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
@@ -3333,7 +3316,7 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -3347,7 +3330,7 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
@@ -3361,7 +3344,7 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
@@ -3375,7 +3358,7 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
@@ -3389,7 +3372,7 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
@@ -3403,7 +3386,7 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
         <v>17</v>
@@ -3417,7 +3400,7 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
@@ -3431,7 +3414,7 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
         <v>19</v>
@@ -3445,7 +3428,7 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
         <v>20</v>
@@ -3459,7 +3442,7 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
@@ -3473,7 +3456,7 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -3487,7 +3470,7 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
         <v>13</v>
@@ -3501,7 +3484,7 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
         <v>14</v>
@@ -3515,7 +3498,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
         <v>15</v>
@@ -3529,7 +3512,7 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C27" t="s">
         <v>16</v>
@@ -3543,7 +3526,7 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
         <v>17</v>
@@ -3557,7 +3540,7 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
         <v>18</v>
@@ -3571,7 +3554,7 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C30" t="s">
         <v>19</v>
@@ -3585,7 +3568,7 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C31" t="s">
         <v>20</v>
@@ -3599,7 +3582,7 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -3613,7 +3596,7 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
@@ -3627,7 +3610,7 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
@@ -3641,7 +3624,7 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
@@ -3655,7 +3638,7 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
@@ -3669,7 +3652,7 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
         <v>16</v>
@@ -3683,7 +3666,7 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C38" t="s">
         <v>17</v>
@@ -3697,7 +3680,7 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
@@ -3711,7 +3694,7 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C40" t="s">
         <v>19</v>
@@ -3725,7 +3708,7 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C41" t="s">
         <v>20</v>
@@ -3739,7 +3722,7 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
@@ -3753,7 +3736,7 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
@@ -3767,7 +3750,7 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
@@ -3781,7 +3764,7 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
@@ -3795,7 +3778,7 @@
         <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C46" t="s">
         <v>15</v>
@@ -3809,7 +3792,7 @@
         <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C47" t="s">
         <v>16</v>
@@ -3823,7 +3806,7 @@
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C48" t="s">
         <v>17</v>
@@ -3837,7 +3820,7 @@
         <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C49" t="s">
         <v>18</v>
@@ -3851,7 +3834,7 @@
         <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C50" t="s">
         <v>19</v>
@@ -3865,7 +3848,7 @@
         <v>9</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C51" t="s">
         <v>20</v>
@@ -3879,7 +3862,7 @@
         <v>9</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C52" t="s">
         <v>11</v>
@@ -3893,7 +3876,7 @@
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C53" t="s">
         <v>12</v>
@@ -3907,7 +3890,7 @@
         <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C54" t="s">
         <v>13</v>
@@ -3921,7 +3904,7 @@
         <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
@@ -3935,7 +3918,7 @@
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C56" t="s">
         <v>15</v>
@@ -3949,7 +3932,7 @@
         <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C57" t="s">
         <v>16</v>
@@ -3963,7 +3946,7 @@
         <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C58" t="s">
         <v>17</v>
@@ -3977,7 +3960,7 @@
         <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C59" t="s">
         <v>18</v>
@@ -3991,7 +3974,7 @@
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C60" t="s">
         <v>19</v>
@@ -4005,7 +3988,7 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C61" t="s">
         <v>20</v>
@@ -4019,7 +4002,7 @@
         <v>10</v>
       </c>
       <c r="B62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C62" t="s">
         <v>11</v>
@@ -4033,7 +4016,7 @@
         <v>10</v>
       </c>
       <c r="B63" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C63" t="s">
         <v>12</v>
@@ -4047,7 +4030,7 @@
         <v>10</v>
       </c>
       <c r="B64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C64" t="s">
         <v>13</v>
@@ -4061,7 +4044,7 @@
         <v>10</v>
       </c>
       <c r="B65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -4075,7 +4058,7 @@
         <v>10</v>
       </c>
       <c r="B66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C66" t="s">
         <v>15</v>
@@ -4089,7 +4072,7 @@
         <v>10</v>
       </c>
       <c r="B67" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C67" t="s">
         <v>16</v>
@@ -4103,7 +4086,7 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C68" t="s">
         <v>17</v>
@@ -4117,7 +4100,7 @@
         <v>10</v>
       </c>
       <c r="B69" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C69" t="s">
         <v>18</v>
@@ -4131,7 +4114,7 @@
         <v>10</v>
       </c>
       <c r="B70" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C70" t="s">
         <v>19</v>
@@ -4145,7 +4128,7 @@
         <v>10</v>
       </c>
       <c r="B71" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C71" t="s">
         <v>20</v>
@@ -4159,7 +4142,7 @@
         <v>10</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
@@ -4173,7 +4156,7 @@
         <v>10</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C73" t="s">
         <v>12</v>
@@ -4187,7 +4170,7 @@
         <v>10</v>
       </c>
       <c r="B74" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C74" t="s">
         <v>13</v>
@@ -4201,7 +4184,7 @@
         <v>10</v>
       </c>
       <c r="B75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
@@ -4215,7 +4198,7 @@
         <v>10</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C76" t="s">
         <v>15</v>
@@ -4229,7 +4212,7 @@
         <v>10</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C77" t="s">
         <v>16</v>
@@ -4243,7 +4226,7 @@
         <v>10</v>
       </c>
       <c r="B78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C78" t="s">
         <v>17</v>
@@ -4257,7 +4240,7 @@
         <v>10</v>
       </c>
       <c r="B79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C79" t="s">
         <v>18</v>
@@ -4271,7 +4254,7 @@
         <v>10</v>
       </c>
       <c r="B80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C80" t="s">
         <v>19</v>
@@ -4285,1864 +4268,13 @@
         <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C81" t="s">
         <v>20</v>
       </c>
       <c r="D81">
         <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D81"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" t="s">
-        <v>23</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="s">
-        <v>24</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" t="s">
-        <v>23</v>
-      </c>
-      <c r="D34">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" t="s">
-        <v>23</v>
-      </c>
-      <c r="D36">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" t="s">
-        <v>24</v>
-      </c>
-      <c r="D37">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38" t="s">
-        <v>19</v>
-      </c>
-      <c r="C38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" t="s">
-        <v>8</v>
-      </c>
-      <c r="B39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40" t="s">
-        <v>23</v>
-      </c>
-      <c r="D40">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" t="s">
-        <v>24</v>
-      </c>
-      <c r="D41">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" t="s">
-        <v>9</v>
-      </c>
-      <c r="B42" t="s">
-        <v>11</v>
-      </c>
-      <c r="C42" t="s">
-        <v>23</v>
-      </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" t="s">
-        <v>9</v>
-      </c>
-      <c r="B43" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" t="s">
-        <v>24</v>
-      </c>
-      <c r="D43">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" t="s">
-        <v>9</v>
-      </c>
-      <c r="B44" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" t="s">
-        <v>23</v>
-      </c>
-      <c r="D44">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" t="s">
-        <v>9</v>
-      </c>
-      <c r="B46" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" t="s">
-        <v>23</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>9</v>
-      </c>
-      <c r="B47" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" t="s">
-        <v>24</v>
-      </c>
-      <c r="D47">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" t="s">
-        <v>9</v>
-      </c>
-      <c r="B48" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48" t="s">
-        <v>23</v>
-      </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" t="s">
-        <v>9</v>
-      </c>
-      <c r="B49" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" t="s">
-        <v>24</v>
-      </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" t="s">
-        <v>15</v>
-      </c>
-      <c r="C50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D50">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" t="s">
-        <v>15</v>
-      </c>
-      <c r="C51" t="s">
-        <v>24</v>
-      </c>
-      <c r="D51">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="s">
-        <v>23</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" t="s">
-        <v>9</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="s">
-        <v>24</v>
-      </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" t="s">
-        <v>9</v>
-      </c>
-      <c r="B54" t="s">
-        <v>17</v>
-      </c>
-      <c r="C54" t="s">
-        <v>23</v>
-      </c>
-      <c r="D54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" t="s">
-        <v>9</v>
-      </c>
-      <c r="B55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C55" t="s">
-        <v>24</v>
-      </c>
-      <c r="D55">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" t="s">
-        <v>9</v>
-      </c>
-      <c r="B56" t="s">
-        <v>18</v>
-      </c>
-      <c r="C56" t="s">
-        <v>23</v>
-      </c>
-      <c r="D56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" t="s">
-        <v>9</v>
-      </c>
-      <c r="B57" t="s">
-        <v>18</v>
-      </c>
-      <c r="C57" t="s">
-        <v>24</v>
-      </c>
-      <c r="D57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" t="s">
-        <v>9</v>
-      </c>
-      <c r="B58" t="s">
-        <v>19</v>
-      </c>
-      <c r="C58" t="s">
-        <v>23</v>
-      </c>
-      <c r="D58">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" t="s">
-        <v>9</v>
-      </c>
-      <c r="B59" t="s">
-        <v>19</v>
-      </c>
-      <c r="C59" t="s">
-        <v>24</v>
-      </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" t="s">
-        <v>9</v>
-      </c>
-      <c r="B60" t="s">
-        <v>20</v>
-      </c>
-      <c r="C60" t="s">
-        <v>23</v>
-      </c>
-      <c r="D60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" t="s">
-        <v>9</v>
-      </c>
-      <c r="B61" t="s">
-        <v>20</v>
-      </c>
-      <c r="C61" t="s">
-        <v>24</v>
-      </c>
-      <c r="D61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" t="s">
-        <v>10</v>
-      </c>
-      <c r="B62" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62" t="s">
-        <v>23</v>
-      </c>
-      <c r="D62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" t="s">
-        <v>10</v>
-      </c>
-      <c r="B63" t="s">
-        <v>11</v>
-      </c>
-      <c r="C63" t="s">
-        <v>24</v>
-      </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" t="s">
-        <v>10</v>
-      </c>
-      <c r="B64" t="s">
-        <v>12</v>
-      </c>
-      <c r="C64" t="s">
-        <v>23</v>
-      </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" t="s">
-        <v>10</v>
-      </c>
-      <c r="B65" t="s">
-        <v>12</v>
-      </c>
-      <c r="C65" t="s">
-        <v>24</v>
-      </c>
-      <c r="D65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" t="s">
-        <v>10</v>
-      </c>
-      <c r="B66" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" t="s">
-        <v>23</v>
-      </c>
-      <c r="D66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" t="s">
-        <v>10</v>
-      </c>
-      <c r="B67" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" t="s">
-        <v>24</v>
-      </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" t="s">
-        <v>10</v>
-      </c>
-      <c r="B68" t="s">
-        <v>14</v>
-      </c>
-      <c r="C68" t="s">
-        <v>23</v>
-      </c>
-      <c r="D68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" t="s">
-        <v>10</v>
-      </c>
-      <c r="B69" t="s">
-        <v>14</v>
-      </c>
-      <c r="C69" t="s">
-        <v>24</v>
-      </c>
-      <c r="D69">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" t="s">
-        <v>10</v>
-      </c>
-      <c r="B70" t="s">
-        <v>15</v>
-      </c>
-      <c r="C70" t="s">
-        <v>23</v>
-      </c>
-      <c r="D70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" t="s">
-        <v>10</v>
-      </c>
-      <c r="B71" t="s">
-        <v>15</v>
-      </c>
-      <c r="C71" t="s">
-        <v>24</v>
-      </c>
-      <c r="D71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" t="s">
-        <v>10</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="s">
-        <v>23</v>
-      </c>
-      <c r="D72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" t="s">
-        <v>10</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="s">
-        <v>24</v>
-      </c>
-      <c r="D73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" t="s">
-        <v>10</v>
-      </c>
-      <c r="B74" t="s">
-        <v>17</v>
-      </c>
-      <c r="C74" t="s">
-        <v>23</v>
-      </c>
-      <c r="D74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" t="s">
-        <v>10</v>
-      </c>
-      <c r="B75" t="s">
-        <v>17</v>
-      </c>
-      <c r="C75" t="s">
-        <v>24</v>
-      </c>
-      <c r="D75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" t="s">
-        <v>10</v>
-      </c>
-      <c r="B76" t="s">
-        <v>18</v>
-      </c>
-      <c r="C76" t="s">
-        <v>23</v>
-      </c>
-      <c r="D76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" t="s">
-        <v>10</v>
-      </c>
-      <c r="B77" t="s">
-        <v>18</v>
-      </c>
-      <c r="C77" t="s">
-        <v>24</v>
-      </c>
-      <c r="D77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" t="s">
-        <v>10</v>
-      </c>
-      <c r="B78" t="s">
-        <v>19</v>
-      </c>
-      <c r="C78" t="s">
-        <v>23</v>
-      </c>
-      <c r="D78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" t="s">
-        <v>10</v>
-      </c>
-      <c r="B79" t="s">
-        <v>19</v>
-      </c>
-      <c r="C79" t="s">
-        <v>24</v>
-      </c>
-      <c r="D79">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" t="s">
-        <v>10</v>
-      </c>
-      <c r="B80" t="s">
-        <v>20</v>
-      </c>
-      <c r="C80" t="s">
-        <v>23</v>
-      </c>
-      <c r="D80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" t="s">
-        <v>10</v>
-      </c>
-      <c r="B81" t="s">
-        <v>20</v>
-      </c>
-      <c r="C81" t="s">
-        <v>24</v>
-      </c>
-      <c r="D81">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2">
-        <v>43</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3">
-        <v>20</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4">
-        <v>73</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5">
-        <v>51</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>50</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7">
-        <v>78</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8">
-        <v>54</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9">
-        <v>10</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10">
-        <v>85</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11">
-        <v>17</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12">
-        <v>86</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13">
-        <v>10</v>
-      </c>
-      <c r="D13">
-        <v>10</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14">
-        <v>76</v>
-      </c>
-      <c r="D14">
-        <v>7</v>
-      </c>
-      <c r="E14">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15">
-        <v>13</v>
-      </c>
-      <c r="D15">
-        <v>7</v>
-      </c>
-      <c r="E15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16">
-        <v>37</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17">
-        <v>64</v>
-      </c>
-      <c r="D17">
-        <v>6</v>
-      </c>
-      <c r="E17">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18">
-        <v>44</v>
-      </c>
-      <c r="D18">
-        <v>5</v>
-      </c>
-      <c r="E18">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19">
-        <v>55</v>
-      </c>
-      <c r="D19">
-        <v>14</v>
-      </c>
-      <c r="E19">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20">
-        <v>82</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21">
-        <v>76</v>
-      </c>
-      <c r="D21">
-        <v>13</v>
-      </c>
-      <c r="E21">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22">
-        <v>9</v>
-      </c>
-      <c r="D22">
-        <v>9</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23">
-        <v>53</v>
-      </c>
-      <c r="D23">
-        <v>4</v>
-      </c>
-      <c r="E23">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24">
-        <v>72</v>
-      </c>
-      <c r="D24">
-        <v>8</v>
-      </c>
-      <c r="E24">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25">
-        <v>84</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26">
-        <v>19</v>
-      </c>
-      <c r="D26">
-        <v>9</v>
-      </c>
-      <c r="E26">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27">
-        <v>40</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28">
-        <v>45</v>
-      </c>
-      <c r="D28">
-        <v>2</v>
-      </c>
-      <c r="E28">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29">
-        <v>88</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30">
-        <v>28</v>
-      </c>
-      <c r="D30">
-        <v>9</v>
-      </c>
-      <c r="E30">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31">
-        <v>70</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" t="s">
-        <v>10</v>
-      </c>
-      <c r="B32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32">
-        <v>70</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33">
-        <v>97</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" t="s">
-        <v>10</v>
-      </c>
-      <c r="B34" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34">
-        <v>78</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" t="s">
-        <v>10</v>
-      </c>
-      <c r="B35" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35">
-        <v>45</v>
-      </c>
-      <c r="D35">
-        <v>2</v>
-      </c>
-      <c r="E35">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" t="s">
-        <v>10</v>
-      </c>
-      <c r="B36" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36">
-        <v>92</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37">
-        <v>82</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" t="s">
-        <v>10</v>
-      </c>
-      <c r="B38" t="s">
-        <v>17</v>
-      </c>
-      <c r="C38">
-        <v>23</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" t="s">
-        <v>10</v>
-      </c>
-      <c r="B39" t="s">
-        <v>18</v>
-      </c>
-      <c r="C39">
-        <v>7</v>
-      </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-      <c r="E39">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" t="s">
-        <v>10</v>
-      </c>
-      <c r="B40" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40">
-        <v>63</v>
-      </c>
-      <c r="D40">
-        <v>7</v>
-      </c>
-      <c r="E40">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" t="s">
-        <v>10</v>
-      </c>
-      <c r="B41" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41">
-        <v>36</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41">
-        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Intelligent_Sourcing.xlsx
+++ b/Intelligent_Sourcing.xlsx
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.99</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="3">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.99</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="4">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Intelligent_Sourcing.xlsx
+++ b/Intelligent_Sourcing.xlsx
@@ -13,6 +13,8 @@
     <sheet name="Cost Data" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Distance Data" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Days Data" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Fulfillment Solution" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Warehouse Stock Status" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +480,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.04</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="3">
@@ -488,7 +490,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4">
@@ -498,7 +500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
@@ -508,7 +510,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -811,57 +813,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Product#1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Product#2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Product#3</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Product#4</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Product#5</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Product#6</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Product#7</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Product#8</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Product#9</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Product#10</t>
         </is>
@@ -873,8 +875,10 @@
           <t>Order#1</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C2" t="n">
         <v>5</v>
@@ -942,7 +946,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -5852,4 +5856,2521 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Supply Quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Product#1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Product#1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Product#2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Product#2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Product#3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Product#3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Product#4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Product#4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Product#5</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Product#5</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Product#6</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Product#6</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Product#7</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Product#7</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Product#8</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Product#8</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Product#9</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Product#9</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Product#10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Product#10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Product#1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Product#1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Product#2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Product#2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Product#3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Product#3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Product#4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Product#4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Product#5</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Product#5</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Product#6</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Product#6</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Product#7</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Product#7</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Product#8</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Product#8</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Product#9</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Product#9</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Product#10</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Product#10</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Product#1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Product#1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Product#2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Product#2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Product#3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Product#3</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Product#4</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Product#4</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Product#5</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Product#5</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Product#6</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Product#6</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Product#7</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Product#7</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Product#8</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Product#8</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Product#9</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Product#9</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Product#10</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Product#10</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Product#1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Product#1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Product#2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Product#2</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Product#3</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Product#3</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Product#4</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Product#4</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Product#5</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Product#5</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Product#6</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Product#6</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Product#7</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Product#7</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Product#8</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Product#8</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Product#9</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Product#9</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Product#10</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Order#1</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Product#10</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Order#2</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Initial Stock</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Supplied Stock</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Remaining Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Product#1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>43</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Product#2</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Product#3</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>73</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Product#4</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>51</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Product#5</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Product#6</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>78</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Product#7</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>54</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Product#8</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Product#9</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>85</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Warehouse#1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Product#10</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Product#1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>86</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Product#2</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Product#3</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>76</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Product#4</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Product#5</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>37</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Product#6</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>64</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Product#7</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>44</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Product#8</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>55</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Product#9</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>82</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Warehouse#2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Product#10</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>76</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Product#1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Product#2</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>53</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Product#3</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>72</v>
+      </c>
+      <c r="D24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Product#4</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>84</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Product#5</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>19</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Product#6</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>40</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Product#7</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>45</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Product#8</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>88</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Product#9</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>28</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Warehouse#3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Product#10</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>70</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Product#1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>70</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Product#2</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>97</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Product#3</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>78</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Product#4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>45</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Product#5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>92</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Product#6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>82</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Product#7</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>23</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Product#8</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>7</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Product#9</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>63</v>
+      </c>
+      <c r="D40" t="n">
+        <v>9</v>
+      </c>
+      <c r="E40" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Warehouse#4</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Product#10</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>36</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>